--- a/order_management/24.1-view-and-manage-all-orders/24.1 - View and manage all orders.xlsx
+++ b/order_management/24.1-view-and-manage-all-orders/24.1 - View and manage all orders.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Endpoints" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Open Questions" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Cross-Epic Dependencies" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Implementation Status" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requirements'!$A$1:$K$15</definedName>
@@ -112,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -154,6 +155,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -521,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -660,6 +667,54 @@
       </c>
       <c r="B13" s="8" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Implementation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Not started — analysis only</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Impl Branch</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Impl Commits</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -673,7 +728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -687,6 +742,7 @@
     <col width="48" customWidth="1" min="9" max="9"/>
     <col width="62" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -745,6 +801,11 @@
           <t>Confluence</t>
         </is>
       </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>Impl Status (2026-07-01)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -798,6 +859,11 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
+      <c r="L2" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -851,6 +917,11 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
+      <c r="L3" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started (Blocked — Booth Build feature (deferred) must ship an order-creation write-path before booth-build orders can appear.)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -904,6 +975,11 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
+      <c r="L4" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -955,6 +1031,11 @@
       <c r="K5" s="10" t="inlineStr">
         <is>
           <t>Open §Order Management → Story 24.1</t>
+        </is>
+      </c>
+      <c r="L5" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
         </is>
       </c>
     </row>
@@ -1006,6 +1087,11 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
+          <t>Out of Scope — —</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1059,6 +1145,11 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
+      <c r="L7" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1112,6 +1203,11 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1165,6 +1261,11 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
+      <c r="L9" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1218,6 +1319,11 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
+      <c r="L10" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1271,6 +1377,11 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
+      <c r="L11" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1324,6 +1435,11 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
+      <c r="L12" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1377,6 +1493,11 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
+      <c r="L13" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1430,6 +1551,11 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
+      <c r="L14" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1481,6 +1607,11 @@
       <c r="K15" s="10" t="inlineStr">
         <is>
           <t>Open §Order Management → Story 24.1</t>
+        </is>
+      </c>
+      <c r="L15" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
         </is>
       </c>
     </row>
@@ -1587,11 +1718,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="120" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1605,6 +1738,16 @@
           <t>Open Question</t>
         </is>
       </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Resolution / Decision</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -1615,6 +1758,16 @@
           <t>An Order has no direct show_id and a Cart/Order is explicitly modeled 'across shows', so an order can reference multiple shows via its line items. How should the single 'Show' column behave for a multi-show order (e.g. join/list multiple show names, show 'Multiple', or is the OM list scoped so each order is effectively single-show)?</t>
         </is>
       </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>OPEN — for team discussion</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>Current direction (2026-07-01): — (pending). Join (orderItem → showProduct → show) is built and can return one or many show names; leaning toward a deduped shows[] array so the UI chooses between listing names and rendering "Multiple". Column contract is a product/UI decision to confirm before coding 24.1-h.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -1623,6 +1776,16 @@
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Is 'sourced from the centralized billing service' a literal architectural requirement (a standalone billing service must exist as the source) or simply a requirement that Total/Balance Due be authoritative? No such service exists today; the figures live on Order.total/paid_amount.</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>OPEN — for team discussion</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Current direction (2026-07-01): — (pending). Leaning that Order.total/paid_amount (frozen at checkout / webhook-maintained) are authoritative and sufficient; authoritative-only confirmation makes 24.1-n fully deliverable, whereas a literal standalone billing-service mandate leaves it Partial (service unbuilt).</t>
         </is>
       </c>
     </row>
@@ -1682,4 +1845,286 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B1" s="16" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>Not started — analysis/feasibility stage only; no branch or SBE ticket cut yet. Extended tracking format applied; per-requirement build status is ◻ Not started.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>Branch / PR</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>— (not started). No SBE ticket / PR / Swagger tag yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Remaining — 24.1-a</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started — OM list endpoint (GET /api/v1/orders).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>Remaining — 24.1-b</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started (Blocked) — include booth-build orders; no producer exists (see Deferred Work).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Remaining — 24.1-c</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started — Order ID + Customer Name clickable cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Remaining — 24.1-d</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started — Company Name column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Remaining — 24.1-f</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started — Item Total column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Remaining — 24.1-g</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started — Balance Due column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Remaining — 24.1-h</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started — Show column (multi-show behavior pending).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Remaining — 24.1-i</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started — Sales Person column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Remaining — 24.1-j</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started — Sales Channel column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Remaining — 24.1-k</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started — Date column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Remaining — 24.1-l</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started — Per-row selection checkbox.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Remaining — 24.1-m</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started — Backend-enforced list data / access (RBAC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Remaining — 24.1-n</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>◻ Not started (Partial) — Total/Balance Due column-accuracy source; figures authoritative but no standalone billing service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Open decision — Show column</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Multi-show "Show" column behavior (join names / "Multiple" / single-show scoping). Gates 24.1-h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>Open decision — Billing service</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>'Centralized billing service' literal vs authoritative. Gates 24.1-n. Figures live on Order.total/paid_amount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Dependency — Booth Build</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>A Booth Build order producer (write-path creating booth-build orders) — needed for 24.1-b. Owner: Order Management / Booth Build (deferred feature).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Dependency — Quick Actions</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Per-row quick-action behaviour (24.1-e, Out of Scope). Owner: Quick Actions Per Order story; list returns only the row id.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>Dependency — Order Details</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>24.1-c click destination page. Owner: separate OM Order Details story; 24.1 owes only the row id/order_number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>Out of API scope</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Front-end row-to-detail / action / checkbox wiring and anything marked Out of Scope are outside API scope.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/order_management/24.1-view-and-manage-all-orders/24.1 - View and manage all orders.xlsx
+++ b/order_management/24.1-view-and-manage-all-orders/24.1 - View and manage all orders.xlsx
@@ -44,7 +44,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -86,8 +86,18 @@
         <fgColor rgb="00BFBFBF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -109,11 +119,25 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -161,6 +185,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -579,7 +612,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>13 requirement(s) to implement here (filter Build Focus = 'Implement here'). 0 covered elsewhere, 1 out of scope.</t>
+          <t>13 requirement(s) to implement here (filter Build Focus = 'Implement here'). 0 covered elsewhere, 1 delegated (24.1-e → 24.5, SBE-1129).</t>
         </is>
       </c>
     </row>
@@ -601,7 +634,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Story 24.1 asks for an admin Order Management list (table) showing all booth, add-on, booth-build, and sponsorship orders with columns for selection checkbox, Order ID + Customer Name (clickable to detail), Company Name, per-row quick links, Item Total, Balance Due, Show, Sales Person, Sales Channel, and Date, with Total/Balance Due "sourced from the centralized billing service" and list/access enforced on the backend. No order-management endpoint exists yet (the admin ppl-order list filters to subscription/ppl_addon and explicitly excludes product orders at ppl-order.service.ts:280), so the OM list API is net-new — but it sits on fully-built primitives: the Order model is written by admin checkout and exhibitor cart/payments with order_type=product, sales_person_id, cart_id, paid_amount (webhook-maintained), and items carry show_product_id. The story is overwhelmingly Deliverable: order_number, billing customer name, company, total, balance-due (total − paid_amount), show (order-item → show_product → show), date, sales channel (from cart.created_by_type + sales_person_id), and the Sales Person column (read of sales_person_id, which is both set at checkout AND admin-reassignable via exhibitor-strategist-assignment) are all backed by real write-paths. Two items fall short — "booth build" orders are explicitly deferred with no producer (Blocked), and the prescribed dedicated "centralized billing service" component does not exist though the figures are authoritative on Order columns (Partial). Quick Links belongs to the separate Quick Actions story (Out of Scope).</t>
+          <t>Story 24.1 asks for an admin Order Management list (table) showing all booth, add-on, booth-build, and sponsorship orders with columns for selection checkbox, Order ID + Customer Name (clickable to detail), Company Name, per-row quick links, Item Total, Balance Due, Show, Sales Person, Sales Channel, and Date, with Total/Balance Due "sourced from the centralized billing service" and list/access enforced on the backend. No order-management endpoint exists yet (the admin ppl-order list filters to subscription/ppl_addon and explicitly excludes product orders at ppl-order.service.ts:280), so the OM list API is net-new — but it sits on fully-built primitives: the Order model is written by admin checkout and exhibitor cart/payments with order_type=product, sales_person_id, cart_id, paid_amount (webhook-maintained), and items carry show_product_id. The story is overwhelmingly Deliverable: order_number, billing customer name, company, total, balance-due (total − paid_amount), show (order-item → show_product → show), date, sales channel (from cart.created_by_type + sales_person_id), and the Sales Person column (read of sales_person_id, which is both set at checkout AND admin-reassignable via exhibitor-strategist-assignment) are all backed by real write-paths. Two items fall short — "booth build" orders are explicitly deferred with no producer (Blocked), and the prescribed dedicated "centralized billing service" component does not exist though the figures are authoritative on Order columns (Partial). Quick Links is Delegated (to 24.5 Quick Actions, SBE-1129, In Progress); 24.1 only returns the row id for the UI to wire those actions.</t>
         </is>
       </c>
     </row>
@@ -626,7 +659,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +669,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -662,7 +695,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Out of Scope</t>
+          <t>Delegated</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
@@ -903,7 +936,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Booth Build feature (deferred) must ship an order-creation write-path before booth-build orders can appear.</t>
+          <t>Booth Build order-producer: SBE-1304 (epic) / SBE-1399 (Create Booth Build Cart/Contract) + SBE-1088 (Original Order Linking, On Hold) — all To Do / On Hold as of 2026-07-01.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -1050,24 +1083,24 @@
           <t>Quick Links (per-row action buttons).</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Out of Scope</t>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>Delegated</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Out of scope</t>
+          <t>Delegated → 24.5</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24.5 Quick Actions Per Order Item (SBE-1129)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>The spec explicitly defers this to the separate 'Quick Actions Per Order' user story. The list endpoint only needs to return the order id so the UI can wire those actions; the actions themselves are not part of this story.</t>
+          <t>Not built in this story — delegated to sibling story 24.5 "Quick Actions Per Order Item" (SBE-1129, In Progress, Admin Panel), which owns and delivers the per-row action behaviour. The 24.1 list endpoint only returns the order id so the UI can wire those actions; the actions themselves are out of 24.1's scope.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1075,7 +1108,11 @@
           <t>story spec 24_1.md:21 ('Quick Links (action buttons) Refer User Story Quick Actions Per Order'); no quick-action code found</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>24.5 Quick Actions Per Order Item (SBE-1129, In Progress)</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -1089,7 +1126,7 @@
       </c>
       <c r="L6" s="15" t="inlineStr">
         <is>
-          <t>Out of Scope — —</t>
+          <t>Delegated → 24.5 Quick Actions Per Order Item (SBE-1129, In Progress); 24.1 only returns the row id</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1274,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>In-scope product orders carry OrderItems with show_product_id, which joins ShowProduct→Shows for the show name; the snapshot is written by checkout. Caveat: there is no direct Order.show_id and a Cart/Order is explicitly modeled 'across shows', so an order can reference multiple shows — the data join is fully built, but the single 'Show' column's behavior for multi-show orders is a product/UI decision (see open question).</t>
+          <t>In-scope product orders carry OrderItems with show_product_id, which joins ShowProduct→Shows for the show name; the snapshot is written by checkout. Caveat: there is no direct Order.show_id and a Cart/Order is explicitly modeled 'across shows', so an order can reference multiple shows — the data join is fully built, but the single 'Show' column's behavior for multi-show orders is a product/UI decision (see open question). Resolved 2026-07-02: the column returns a deduped shows[] array (FE renders list vs 'Multiple').</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1263,7 +1300,7 @@
       </c>
       <c r="L9" s="15" t="inlineStr">
         <is>
-          <t>◻ Not started</t>
+          <t>Deliverable — deduped shows[] array (multi-show resolved 2026-07-02).</t>
         </is>
       </c>
     </row>
@@ -1568,9 +1605,9 @@
           <t>Total and Balance Due shall be sourced from the centralized billing service (column accuracy).</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Deliverable</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1585,7 +1622,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>The numeric values are accurate and available now from Order.total and Order.paid_amount (frozen at checkout / webhook-maintained), so the columns themselves can be delivered. However, no dedicated 'centralized billing service' component exists — pricing is computed by an in-process cart-pricing service and totals are frozen onto Order columns. If the spec literally requires a standalone billing service as the source of truth, that service is unbuilt; if it only requires authoritative figures, those exist.</t>
+          <t>Resolved 2026-07-02: the team confirmed authoritative figures — not a literal standalone service — satisfy the requirement. Total/Balance Due read from Order.total and Order.paid_amount (frozen at checkout / webhook-maintained), the authoritative source of truth; no dedicated 'centralized billing service' component is required. The numeric values are accurate and available now from Order.total and Order.paid_amount (frozen at checkout / webhook-maintained), so the columns themselves can be delivered. However, no dedicated 'centralized billing service' component exists — pricing is computed by an in-process cart-pricing service and totals are frozen onto Order columns. If the spec literally requires a standalone billing service as the source of truth, that service is unbuilt; if it only requires authoritative figures, those exist.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1611,7 +1648,7 @@
       </c>
       <c r="L15" s="15" t="inlineStr">
         <is>
-          <t>◻ Not started</t>
+          <t>Deliverable — authoritative figures on Order.total/paid_amount (resolved 2026-07-02).</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1760,12 +1797,12 @@
       </c>
       <c r="C2" s="15" t="inlineStr">
         <is>
-          <t>OPEN — for team discussion</t>
+          <t>RESOLVED (2026-07-02)</t>
         </is>
       </c>
       <c r="D2" s="15" t="inlineStr">
         <is>
-          <t>Current direction (2026-07-01): — (pending). Join (orderItem → showProduct → show) is built and can return one or many show names; leaning toward a deduped shows[] array so the UI chooses between listing names and rendering "Multiple". Column contract is a product/UI decision to confirm before coding 24.1-h.</t>
+          <t>Decision: endpoint returns a deduped shows[] array (join orderItem→showProduct→show); FE renders list vs 'Multiple'. 24.1-h Deliverable.</t>
         </is>
       </c>
     </row>
@@ -1780,12 +1817,34 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>OPEN — for team discussion</t>
+          <t>RESOLVED (2026-07-02)</t>
         </is>
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>Current direction (2026-07-01): — (pending). Leaning that Order.total/paid_amount (frozen at checkout / webhook-maintained) are authoritative and sufficient; authoritative-only confirmation makes 24.1-n fully deliverable, whereas a literal standalone billing-service mandate leaves it Partial (service unbuilt).</t>
+          <t>Decision: authoritative figures on Order.total/paid_amount satisfy the requirement; no standalone billing service mandated. 24.1-n Deliverable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>24.1-b</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Booth-build orders cannot appear in the OM list until the Booth Build feature ships an order-producer (no OrderType.booth_build, no write-path today).</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>Blocked (2026-07-01)</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>Booth-build orders cannot appear until a producer writes them: no booth_build value in OrderType and no write-path today (only the nullable parent_cart_id placeholder). Owning stories (Jira, 2026-07-01): SBE-1304 'Booth Build Cart/Contract Creation' (epic, To Do) / SBE-1399 'Create Booth Build Cart/Contract' (story, To Do, Admin API) as the order-producer, plus SBE-1088 'Original Order Linking Workflow' (On Hold, Manish Gun); related SBE-1079 (Share Cart epic), SBE-1086 (Unified Signing, On Hold). Undecided whether booth-build is a distinct order_type or a product order. OM list surfaces it automatically once written.</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1897,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Order Management / Booth Build (deferred feature)</t>
+          <t>Booth Build feature — SBE-1304 (epic) / SBE-1399 (Create Booth Build Cart/Contract, To Do, Admin API) + SBE-1088 (Original Order Linking, On Hold, Manish Gun). Not built 2026-07-01.</t>
         </is>
       </c>
     </row>
@@ -2091,12 +2150,12 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>Dependency — Quick Actions</t>
+          <t>Dependency — Quick Actions (Delegated → 24.5)</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Per-row quick-action behaviour (24.1-e, Out of Scope). Owner: Quick Actions Per Order story; list returns only the row id.</t>
+          <t>Per-row quick-action behaviour (24.1-e, Delegated to 24.5 Quick Actions, SBE-1129, In Progress). Owner: story 24.5 "Quick Actions Per Order Item"; list returns only the row id.</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2179,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Front-end row-to-detail / action / checkbox wiring and anything marked Out of Scope are outside API scope.</t>
+          <t>Front-end row-to-detail / action / checkbox wiring and anything Delegated or out of scope are outside API scope.</t>
         </is>
       </c>
     </row>

--- a/order_management/24.1-view-and-manage-all-orders/24.1 - View and manage all orders.xlsx
+++ b/order_management/24.1-view-and-manage-all-orders/24.1 - View and manage all orders.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,8 +43,12 @@
       <color rgb="000563C1"/>
       <u val="single"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -96,6 +100,11 @@
         <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -137,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -195,6 +204,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -710,7 +725,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Not started — analysis only</t>
+          <t>12 of 14 reqs shipped in SBE-1125 (GET /api/v1/orders); 24.1-b Blocked (booth-build), 24.1-e Delegated → 24.5 (SBE-1129)</t>
         </is>
       </c>
     </row>
@@ -722,7 +737,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SBE-1125 (admin-backend-api)</t>
         </is>
       </c>
     </row>
@@ -734,7 +749,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6dc3104 (feat — OM list endpoint), b95627b (SonarQube S7781 fix)</t>
         </is>
       </c>
     </row>
@@ -746,7 +761,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bitbucket #513 → dev</t>
         </is>
       </c>
     </row>
@@ -836,7 +851,7 @@
       </c>
       <c r="L1" s="9" t="inlineStr">
         <is>
-          <t>Impl Status (2026-07-01)</t>
+          <t>Impl Status (2026-07-02)</t>
         </is>
       </c>
     </row>
@@ -892,9 +907,9 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
-      <c r="L2" s="15" t="inlineStr">
-        <is>
-          <t>◻ Not started</t>
+      <c r="L2" s="20" t="inlineStr">
+        <is>
+          <t>✅ Done — GET /api/v1/orders (paginated, product-scoped, wrapped envelope).</t>
         </is>
       </c>
     </row>
@@ -950,9 +965,9 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
-      <c r="L3" s="15" t="inlineStr">
-        <is>
-          <t>◻ Not started (Blocked — Booth Build feature (deferred) must ship an order-creation write-path before booth-build orders can appear.)</t>
+      <c r="L3" s="20" t="inlineStr">
+        <is>
+          <t>⛔ Blocked — no booth-build producer (SBE-1304/1399/1088); list auto-surfaces once one writes order_type=product.</t>
         </is>
       </c>
     </row>
@@ -1008,9 +1023,9 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
-      <c r="L4" s="15" t="inlineStr">
-        <is>
-          <t>◻ Not started</t>
+      <c r="L4" s="20" t="inlineStr">
+        <is>
+          <t>✅ Done — row id + order_number + customer_name (billing snapshot).</t>
         </is>
       </c>
     </row>
@@ -1066,9 +1081,9 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
-      <c r="L5" s="15" t="inlineStr">
-        <is>
-          <t>◻ Not started</t>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>✅ Done — company_name = billing_company_name (blank → Company.name fallback).</t>
         </is>
       </c>
     </row>
@@ -1124,9 +1139,9 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
-      <c r="L6" s="15" t="inlineStr">
-        <is>
-          <t>Delegated → 24.5 Quick Actions Per Order Item (SBE-1129, In Progress); 24.1 only returns the row id</t>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>Delegated → 24.5 Quick Actions (SBE-1129) — list returns row id only.</t>
         </is>
       </c>
     </row>
@@ -1182,9 +1197,9 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
-      <c r="L7" s="15" t="inlineStr">
-        <is>
-          <t>◻ Not started</t>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>✅ Done — item_total = Order.total (2-dp string).</t>
         </is>
       </c>
     </row>
@@ -1240,9 +1255,9 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
-      <c r="L8" s="15" t="inlineStr">
-        <is>
-          <t>◻ Not started</t>
+      <c r="L8" s="20" t="inlineStr">
+        <is>
+          <t>✅ Done — balance_due = total − paid_amount, floored at 0.</t>
         </is>
       </c>
     </row>
@@ -1298,9 +1313,9 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
-      <c r="L9" s="15" t="inlineStr">
-        <is>
-          <t>Deliverable — deduped shows[] array (multi-show resolved 2026-07-02).</t>
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>✅ Done — deduped shows[] (id/title/city/date), [] when none.</t>
         </is>
       </c>
     </row>
@@ -1356,9 +1371,9 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
-      <c r="L10" s="15" t="inlineStr">
-        <is>
-          <t>◻ Not started</t>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>✅ Done — sales_person (User join), null for self-service.</t>
         </is>
       </c>
     </row>
@@ -1414,9 +1429,9 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
-      <c r="L11" s="15" t="inlineStr">
-        <is>
-          <t>◻ Not started</t>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>✅ Done — sales_channel from cart.created_by_type (exhibitor→self_service, else admin_sales).</t>
         </is>
       </c>
     </row>
@@ -1472,9 +1487,9 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
-      <c r="L12" s="15" t="inlineStr">
-        <is>
-          <t>◻ Not started</t>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>✅ Done — order_date = Order.created_at.</t>
         </is>
       </c>
     </row>
@@ -1530,9 +1545,9 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
-      <c r="L13" s="15" t="inlineStr">
-        <is>
-          <t>◻ Not started</t>
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>✅ Done — selectable rows surfaced via row id.</t>
         </is>
       </c>
     </row>
@@ -1588,9 +1603,9 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
-      <c r="L14" s="15" t="inlineStr">
-        <is>
-          <t>◻ Not started</t>
+      <c r="L14" s="20" t="inlineStr">
+        <is>
+          <t>✅ Done — @Permissions('orders.list') + JWT guard; orders.list seeded (Admin + Super Administrator).</t>
         </is>
       </c>
     </row>
@@ -1646,9 +1661,9 @@
           <t>Open §Order Management → Story 24.1</t>
         </is>
       </c>
-      <c r="L15" s="15" t="inlineStr">
-        <is>
-          <t>Deliverable — authoritative figures on Order.total/paid_amount (resolved 2026-07-02).</t>
+      <c r="L15" s="20" t="inlineStr">
+        <is>
+          <t>✅ Done — authoritative Order.total/paid_amount (no standalone billing service).</t>
         </is>
       </c>
     </row>
@@ -1912,274 +1927,190 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="B1" s="16" t="inlineStr">
+      <c r="B1" s="21" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
-        <is>
-          <t>Not started — analysis/feasibility stage only; no branch or SBE ticket cut yet. Extended tracking format applied; per-requirement build status is ◻ Not started.</t>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>Shipped — built, live-smoke-tested, code-reviewed; all gates green; PR open against dev (not yet merged).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>Branch / PR</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="inlineStr">
-        <is>
-          <t>— (not started). No SBE ticket / PR / Swagger tag yet.</t>
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>SBE-1125 (admin-backend-api)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>Remaining — 24.1-a</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>◻ Not started — OM list endpoint (GET /api/v1/orders).</t>
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>SBE ticket</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>SBE-1125</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Commits</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>6dc3104 (feat — OM list endpoint), b95627b (SonarQube S7781 fix)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Bitbucket #513 → dev</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Swagger tag</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Admin - Order Management (/api/docs/admin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>Build gates</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Pipeline #838 SUCCESSFUL — gitleaks + lint/typecheck/test (2702 pass; orders module 48) + SonarQube quality gate all green</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>Live smoke</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>RBAC/validation matrix + 32-assertion self-cleaning seeded fixture (exhibitor/admin/null-cart orders, subscription exclusion, derivations, filters, sort, search) — all passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Confirmed build scope</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>GET /api/v1/orders — 24.1-a,c,d,f,g,h,i,j,k,l,m,n shipped (12 of 14). Row: id, order_number, customer_name, company_name, item_total, balance_due, shows[], sales_person, sales_channel, order_date, status, currency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Remaining — 24.1-b</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>◻ Not started (Blocked) — include booth-build orders; no producer exists (see Deferred Work).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>Remaining — 24.1-c</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>◻ Not started — Order ID + Customer Name clickable cell.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>Remaining — 24.1-d</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>◻ Not started — Company Name column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>Remaining — 24.1-f</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>◻ Not started — Item Total column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>Remaining — 24.1-g</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>◻ Not started — Balance Due column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>Remaining — 24.1-h</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>◻ Not started — Show column (multi-show behavior pending).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>Remaining — 24.1-i</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>◻ Not started — Sales Person column.</t>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Blocked — booth-build orders; no producer (SBE-1304/1399/1088). No OM-list change needed: the list surfaces the order once it lands as order_type=product.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Remaining — 24.1-j</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>◻ Not started — Sales Channel column.</t>
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>Delegated — 24.1-e</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Quick Links → story 24.5 Quick Actions Per Order Item (SBE-1129, In Progress); the list only returns the row id.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>Remaining — 24.1-k</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>◻ Not started — Date column.</t>
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Dependency — Booth Build</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Booth Build order producer (write-path creating booth-build orders) — needed for 24.1-b. Owner: SBE-1304/1399/1088 (deferred).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>Remaining — 24.1-l</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>◻ Not started — Per-row selection checkbox.</t>
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Dependency — Order Details</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>24.1-c click destination page — owner: OM Order Details story; the list owes only row id/order_number (shipped).</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>Remaining — 24.1-m</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>◻ Not started — Backend-enforced list data / access (RBAC).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Remaining — 24.1-n</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>◻ Not started (Partial) — Total/Balance Due column-accuracy source; figures authoritative but no standalone billing service.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>Open decision — Show column</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>Multi-show "Show" column behavior (join names / "Multiple" / single-show scoping). Gates 24.1-h.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>Open decision — Billing service</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>'Centralized billing service' literal vs authoritative. Gates 24.1-n. Figures live on Order.total/paid_amount.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Dependency — Booth Build</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>A Booth Build order producer (write-path creating booth-build orders) — needed for 24.1-b. Owner: Order Management / Booth Build (deferred feature).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>Dependency — Quick Actions (Delegated → 24.5)</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>Per-row quick-action behaviour (24.1-e, Delegated to 24.5 Quick Actions, SBE-1129, In Progress). Owner: story 24.5 "Quick Actions Per Order Item"; list returns only the row id.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>Dependency — Order Details</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>24.1-c click destination page. Owner: separate OM Order Details story; 24.1 owes only the row id/order_number.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>Out of API scope</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>Front-end row-to-detail / action / checkbox wiring and anything Delegated or out of scope are outside API scope.</t>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Front-end row-to-detail / action / checkbox wiring.</t>
         </is>
       </c>
     </row>

--- a/order_management/24.1-view-and-manage-all-orders/24.1 - View and manage all orders.xlsx
+++ b/order_management/24.1-view-and-manage-all-orders/24.1 - View and manage all orders.xlsx
@@ -146,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -210,6 +210,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -725,7 +731,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12 of 14 reqs shipped in SBE-1125 (GET /api/v1/orders); 24.1-b Blocked (booth-build), 24.1-e Delegated → 24.5 (SBE-1129)</t>
+          <t>Delivered — merged to dev (PR #513, OM Phase-1 one-release). balance_due re-aligned to net-of-refund 2026-07-05 (P1 fix 7fd7a9b / PR#539 -&gt; dev 55c6e61).</t>
         </is>
       </c>
     </row>
@@ -851,7 +857,7 @@
       </c>
       <c r="L1" s="9" t="inlineStr">
         <is>
-          <t>Impl Status (2026-07-02)</t>
+          <t>Impl Status (2026-07-05)</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1263,7 @@
       </c>
       <c r="L8" s="20" t="inlineStr">
         <is>
-          <t>✅ Done — balance_due = total − paid_amount, floored at 0.</t>
+          <t>✅ Done — balance_due = total - NET paid (net = paid_amount - Σ succeeded refunds), floored at 0. Re-aligned to the 24.6 canonical net balance 2026-07-05 (P1 fix 7fd7a9b / PR#539 -&gt; dev 55c6e61; was gross at first ship).</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1954,7 +1960,7 @@
       </c>
       <c r="B2" s="17" t="inlineStr">
         <is>
-          <t>Shipped — built, live-smoke-tested, code-reviewed; all gates green; PR open against dev (not yet merged).</t>
+          <t>Delivered — merged to dev 2026-07-05 (PR #513, OM Phase-1 one-release on feature/SBE-1125). Built, live-smoke-tested, code-reviewed; all gates green.</t>
         </is>
       </c>
     </row>
@@ -2111,6 +2117,18 @@
       <c r="B15" s="17" t="inlineStr">
         <is>
           <t>Front-end row-to-detail / action / checkbox wiring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>Post-merge fix (P1)</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>balance_due changed from gross (total - paid_amount) to NET-of-refund (deriveNetPaid) to match the 24.6 canonical balance — fix(SBE-1131) 7fd7a9b, admin PR#539 -&gt; dev 55c6e61 (2026-07-05).</t>
         </is>
       </c>
     </row>
